--- a/query7_results.xlsx
+++ b/query7_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5285cb0be836e74d/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5285cb0be836e74d/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F60335CA-0D3D-48C1-9108-08BA361727D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7073C0EB-D5F6-4D41-B8AC-F43AC124F6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3660" windowWidth="21600" windowHeight="11295" xr2:uid="{87520124-4EC6-4170-BC19-DEA58A91864F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{035CABA3-18A2-4805-8428-C66EB1F5CEAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
   <si>
     <t>Sport</t>
   </si>
@@ -47,16 +50,25 @@
     <t>entries</t>
   </si>
   <si>
+    <t>total_invested</t>
+  </si>
+  <si>
+    <t>total_winnings</t>
+  </si>
+  <si>
     <t>total_profit</t>
   </si>
   <si>
-    <t>avg_roi_pct</t>
+    <t>portfolio_roi_pct</t>
+  </si>
+  <si>
+    <t>avg_entry_roi_pct</t>
   </si>
   <si>
     <t>NFL</t>
   </si>
   <si>
-    <t>Other</t>
+    <t>Tournament (GPP)</t>
   </si>
   <si>
     <t>MLB</t>
@@ -68,25 +80,22 @@
     <t>CS:GO</t>
   </si>
   <si>
+    <t>50/50</t>
+  </si>
+  <si>
     <t>NHL</t>
   </si>
   <si>
     <t>Double Up</t>
   </si>
   <si>
-    <t>50/50</t>
+    <t>Small League (3-19)</t>
+  </si>
+  <si>
+    <t>Multiplier (Triple/Quintuple Up)</t>
   </si>
   <si>
     <t>Head-to-Head</t>
-  </si>
-  <si>
-    <t>GPP/Major Tournament</t>
-  </si>
-  <si>
-    <t>COD</t>
-  </si>
-  <si>
-    <t>IRACE</t>
   </si>
 </sst>
 </file>
@@ -461,11 +470,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D72779-3C18-4153-9117-904762EE86CC}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2599638-6085-4A3F-95C5-A07BA4587CBF}">
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -481,260 +500,404 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>3562</v>
+        <v>1762</v>
       </c>
       <c r="D2" s="1">
-        <v>59006.86</v>
-      </c>
-      <c r="E2">
-        <v>72.62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31427</v>
+      </c>
+      <c r="E2" s="1">
+        <v>85651.89</v>
+      </c>
+      <c r="F2" s="1">
+        <v>54224.89</v>
+      </c>
+      <c r="G2">
+        <v>172.54</v>
+      </c>
+      <c r="H2">
+        <v>101.47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>14571</v>
+        <v>12423</v>
       </c>
       <c r="D3" s="1">
-        <v>34515.879999999997</v>
-      </c>
-      <c r="E3">
-        <v>51.78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39915.550000000003</v>
+      </c>
+      <c r="E3" s="1">
+        <v>72220.850000000006</v>
+      </c>
+      <c r="F3" s="1">
+        <v>32305.3</v>
+      </c>
+      <c r="G3">
+        <v>80.930000000000007</v>
+      </c>
+      <c r="H3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>5567</v>
+        <v>4147</v>
       </c>
       <c r="D4" s="1">
-        <v>22652.91</v>
-      </c>
-      <c r="E4">
-        <v>36.520000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>50542.99</v>
+      </c>
+      <c r="E4" s="1">
+        <v>72540.759999999995</v>
+      </c>
+      <c r="F4" s="1">
+        <v>21997.77</v>
+      </c>
+      <c r="G4">
+        <v>43.52</v>
+      </c>
+      <c r="H4">
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
       </c>
       <c r="C5">
         <v>37</v>
       </c>
       <c r="D5" s="1">
+        <v>412</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2668</v>
+      </c>
+      <c r="F5" s="1">
         <v>2256</v>
       </c>
-      <c r="E5">
+      <c r="G5">
+        <v>547.57000000000005</v>
+      </c>
+      <c r="H5">
         <v>501.58</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>517</v>
+        <v>780</v>
       </c>
       <c r="D6" s="1">
-        <v>2000.89</v>
-      </c>
-      <c r="E6">
-        <v>40.76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3117</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4843.37</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1726.37</v>
+      </c>
+      <c r="G6">
+        <v>55.39</v>
+      </c>
+      <c r="H6">
+        <v>45.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>382</v>
       </c>
       <c r="D7" s="1">
+        <v>1845</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3401.01</v>
+      </c>
+      <c r="F7" s="1">
         <v>1556.01</v>
       </c>
-      <c r="E7">
+      <c r="G7">
+        <v>84.34</v>
+      </c>
+      <c r="H7">
         <v>81.94</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>203</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1474</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2664.3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1190.3</v>
+      </c>
+      <c r="G8">
+        <v>80.75</v>
+      </c>
+      <c r="H8">
+        <v>-13.36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>171</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1047</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2171.66</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1124.6600000000001</v>
+      </c>
+      <c r="G9">
+        <v>107.42</v>
+      </c>
+      <c r="H9">
+        <v>69.78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>844</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3885</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4895.1000000000004</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1010.1</v>
+      </c>
+      <c r="G10">
+        <v>26</v>
+      </c>
+      <c r="H10">
+        <v>16.670000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
         <v>462</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D11" s="1">
+        <v>2914</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3638</v>
+      </c>
+      <c r="F11" s="1">
         <v>724</v>
       </c>
-      <c r="E8">
+      <c r="G11">
+        <v>24.85</v>
+      </c>
+      <c r="H11">
         <v>4.76</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1">
-        <v>50.8</v>
-      </c>
-      <c r="E9">
-        <v>52.73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>269</v>
-      </c>
-      <c r="D10" s="1">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="E10">
-        <v>6.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>54</v>
-      </c>
-      <c r="D11" s="1">
-        <v>-19.2</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12">
-        <v>50</v>
+        <v>523</v>
       </c>
       <c r="D12" s="1">
-        <v>-24</v>
-      </c>
-      <c r="E12">
-        <v>-9.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3453</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4108.7</v>
+      </c>
+      <c r="F12" s="1">
+        <v>655.7</v>
+      </c>
+      <c r="G12">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="H12">
+        <v>36.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="D13" s="1">
-        <v>-35</v>
-      </c>
-      <c r="E13">
-        <v>-16.670000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1913</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2528.5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>615.5</v>
+      </c>
+      <c r="G13">
+        <v>32.17</v>
+      </c>
+      <c r="H13">
+        <v>47.06</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D14" s="1">
-        <v>-36</v>
-      </c>
-      <c r="E14">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1191.4000000000001</v>
+      </c>
+      <c r="F14" s="1">
+        <v>614.4</v>
+      </c>
+      <c r="G14">
+        <v>106.48</v>
+      </c>
+      <c r="H14">
+        <v>96.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="D15" s="1">
-        <v>-61.89</v>
-      </c>
-      <c r="E15">
-        <v>-15.26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2588.25</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3200.58</v>
+      </c>
+      <c r="F15" s="1">
+        <v>612.33000000000004</v>
+      </c>
+      <c r="G15">
+        <v>23.66</v>
+      </c>
+      <c r="H15">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C16">
-        <v>20</v>
+        <v>1640</v>
       </c>
       <c r="D16" s="1">
-        <v>-200</v>
-      </c>
-      <c r="E16">
-        <v>-100</v>
+        <v>7810</v>
+      </c>
+      <c r="E16" s="1">
+        <v>8381.7000000000007</v>
+      </c>
+      <c r="F16" s="1">
+        <v>571.70000000000005</v>
+      </c>
+      <c r="G16">
+        <v>7.32</v>
+      </c>
+      <c r="H16">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
